--- a/output/pdf_financials_xlsx/SHLL.P.xlsx
+++ b/output/pdf_financials_xlsx/SHLL.P.xlsx
@@ -2677,16 +2677,16 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.06153</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.06153</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.065618</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.065618</v>
       </c>
     </row>
     <row r="93">
@@ -4082,7 +4082,11 @@
           <t>Reserves (Note 4)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -4293,7 +4297,11 @@
           <t>Reserves (note 5)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -4498,7 +4506,11 @@
           <t>Reserves (note 5c)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SHLL.P.xlsx
+++ b/output/pdf_financials_xlsx/SHLL.P.xlsx
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.033425</v>
+        <v>0.130457</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.02955</v>
+        <v>0.080695</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.039258</v>
+        <v>0.116691</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.016037</v>
+        <v>0.062305</v>
       </c>
     </row>
     <row r="11">
@@ -666,16 +666,16 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.033425</v>
+        <v>-0.130457</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.02955</v>
+        <v>-0.080695</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.039258</v>
+        <v>-0.116691</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.016037</v>
+        <v>-0.062305</v>
       </c>
     </row>
     <row r="12">
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.003823</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000712</v>
       </c>
     </row>
     <row r="13">
@@ -1076,10 +1076,10 @@
         <v>-0.330695</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.112868</v>
+        <v>-0.116691</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.059741</v>
+        <v>-0.060453</v>
       </c>
     </row>
     <row r="28">
@@ -1124,10 +1124,10 @@
         <v>-0.330695</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.112868</v>
+        <v>-0.116691</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.059741</v>
+        <v>-0.060453</v>
       </c>
     </row>
     <row r="30">
@@ -1237,16 +1237,16 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.486849</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.154839</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.048485</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.006675</v>
       </c>
     </row>
     <row r="35">
@@ -1285,16 +1285,16 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.486849</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.154839</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.048485</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.006675</v>
       </c>
     </row>
     <row r="37">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">

--- a/output/pdf_financials_xlsx/SHLL.P.xlsx
+++ b/output/pdf_financials_xlsx/SHLL.P.xlsx
@@ -5262,7 +5262,11 @@
           <t>Proceeds from shares issued</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
